--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_608_Philippines.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_608_Philippines.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf3ff8f9a17394b44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rfe3c838d09c24f28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R4756dce31d714ed7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R6906d5b0635e4a31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rde7e57dcb33e49be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R0a43eb6ac7144f06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R6686b8be51c24dcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9d8d545d79674069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf85bdda61acb4c6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R36fd9ee556664444"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rdf9b9e103b734ce7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R36b31de58c87472a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ608CommercialTable" displayName="EEZ608CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ608CommercialTable" displayName="EEZ608CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ608FunctionalTable" displayName="EEZ608FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ608FunctionalTable" displayName="EEZ608FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ608ValidationTable" displayName="EEZ608ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ608ValidationTable" displayName="EEZ608ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -12218,7 +12172,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec3443651c434820"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53b4a119da444be7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12228,20 +12182,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -12249,606 +12193,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>40167.316221059096</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>40167.316221059096</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$173,A2,'Species'!$U$2:$U$173))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>6366090.603818945</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>6366090.603818945</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>52188.17601400799</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.7588733159117584</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>57.39490163457966</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>52188.17601400799</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>84.16730670888273</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$173,A3,'Species'!$U$2:$U$173))</x:f>
-        <x:v>4392538.217148168</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.7588733159117584</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>57.39490163457966</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2995335.2288121185</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1397202.9883360495</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.4664596386061763</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.4664596386061764</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1124.4953723791</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.058196871183961</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1143.3965334443915</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1124.4953723791</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1145.2957786348377</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$173,A4,'Species'!$U$2:$U$173))</x:f>
-        <x:v>1287879.803080193</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.058196871183961</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1143.3965334443915</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1285744.110652523</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2135.6924276698846</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0016610555786143</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0016610555786143227</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>348944.37214234704</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.7741061003104046</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>59.443736489386964</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>348944.37214234704</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>71.90048600871555</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$173,A5,'Species'!$U$2:$U$173))</x:f>
-        <x:v>25089269.947040856</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.7741061003104046</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>59.443736489386964</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>20742557.30708426</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>4346712.639956597</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2095552913560979</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.2095552913560978</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>5710.407158962001</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.138284554155425</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>13.749425562726826</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>5710.407158962001</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>14.173797152149406</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$173,A6,'Species'!$U$2:$U$173))</x:f>
-        <x:v>80938.15272730919</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.138284554155425</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>13.749425562726826</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>78514.8181650104</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2423.334562298798</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0308646777631938</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.030864677763193765</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>767776.8918181022</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.1065320707609367</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>127.80035810946663</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>767776.8918181022</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>214.40885528944548</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$173,A7,'Species'!$U$2:$U$173))</x:f>
-        <x:v>164618164.4924077</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.1065320707609367</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>127.80035810946663</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>98122161.72252668</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>66496002.769881025</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.6776858724119916</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.6776858724119916</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>736737.6178373733</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5017007806311335</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>317.4686027964406</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>736737.6178373733</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>559.4869901599188</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$173,A8,'Species'!$U$2:$U$173))</x:f>
-        <x:v>412195112.34142053</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5017007806311335</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>317.4686027964406</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>233891062.16240892</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>178304050.1790116</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.7623380240806343</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.7623380240806342</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>279.86286805000003</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>398.1071705534973</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>279.86286805000003</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>398.1071705534973</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$173,A9,'Species'!$U$2:$U$173))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>111415.41454237228</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>398.1071705534973</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>111415.41454237228</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4520.9815437157</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.104663732225143</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1272.51740811783</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4520.9815437157</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1363.5230160343456</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$173,A10,'Species'!$U$2:$U$173))</x:f>
-        <x:v>6164462.389922843</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.104663732225143</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1272.51740811783</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>5753027.716157649</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>411434.6737651946</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0715161987851476</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.07151619878514769</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>194751.92085138403</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.404660447110555</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2538.9868239407288</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>194751.92085138403</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2554.1598611290015</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$173,A11,'Species'!$U$2:$U$173))</x:f>
-        <x:v>497427539.1163773</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.404660447110555</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2538.9868239407288</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>494472560.97881174</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2954978.137565553</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0059760204524113</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.005976020452411261</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3e1a91fe02d4db5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24e386aeda1f401e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12858,20 +12408,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -12879,1146 +12419,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>48642.990825197</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8708461119425057</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>742.7559028775688</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>48642.990825197</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>754.9323221823042</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$173,A2,'Species'!$U$2:$U$173))</x:f>
-        <x:v>36722166.021558486</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8708461119425057</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>742.7559028775688</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>36129868.569034494</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>592297.4525239915</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0163935678700926</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.016393567870092576</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1241</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4599999999999995</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.4031503126603</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1241</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$173,A3,'Species'!$U$2:$U$173))</x:f>
-        <x:v>357908.30953801173</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4599999999999995</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.4031503126603</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>357908.3095380114</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>3.4924596548080444e-10</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>9.757973094606596e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>6.277016957</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.22</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1659.5869074375596</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>6.277016957</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1659.5869074375596</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$173,A4,'Species'!$U$2:$U$173))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>10417.25515960075</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.22</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1659.5869074375596</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>10417.25515960075</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>13135.4347936499</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.303732784044398</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2012.4856116497406</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>13135.4347936499</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2487.4263028459527</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$173,A5,'Species'!$U$2:$U$173))</x:f>
-        <x:v>32673426.00504266</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.303732784044398</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2012.4856116497406</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>26434873.5249838</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>6238552.48005886</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2359970617662595</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.2359970617662595</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1930.1637428889999</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.145168378758745</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1396.9098469960181</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1930.1637428889999</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1470.8921849533922</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$173,A6,'Species'!$U$2:$U$173))</x:f>
-        <x:v>2839062.7650958183</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.145168378758745</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1396.9098469960181</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2696264.7387563344</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>142798.0263394839</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0529614263343259</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.052961426334325844</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>125259.157953999</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.43691242546511</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2734.7172209416613</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>125259.157953999</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2772.369911164394</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$173,A7,'Species'!$U$2:$U$173))</x:f>
-        <x:v>347264720.60945505</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.43691242546511</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2734.7172209416613</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>342548376.33745277</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4716344.27200228</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0137684035242838</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.013768403524283804</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>22446.467692639097</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.216852362107171</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1647.602195904176</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>22446.467692639097</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1653.8393212993976</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$173,A8,'Species'!$U$2:$U$173))</x:f>
-        <x:v>37122850.8943631</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.216852362107171</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1647.602195904176</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>36982849.460684314</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>140001.43367878348</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0037855772532513</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0037855772532512954</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4520.9815437157</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.104663732225143</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1272.51740811783</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4520.9815437157</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1363.5230160343456</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$173,A9,'Species'!$U$2:$U$173))</x:f>
-        <x:v>6164462.389922843</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.104663732225143</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1272.51740811783</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>5753027.716157649</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>411434.6737651946</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0715161987851476</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.07151619878514769</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>28832.923866421002</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.573397918787624</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>37.44535211372505</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>28832.923866421002</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>52.40963306847066</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$173,A10,'Species'!$U$2:$U$173))</x:f>
-        <x:v>1511122.9601302752</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.573397918787624</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>37.44535211372505</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1079658.9866463612</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>431463.97348391404</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.3996298635221185</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.3996298635221185</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>2.3443296951</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.117594974834903</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>131.09767054206685</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>2.3443296951</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>143.12244298456565</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$173,A11,'Species'!$U$2:$U$173))</x:f>
-        <x:v>335.5261931239739</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.117594974834903</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>131.09767054206685</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>307.3361620102038</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>28.19003111377009</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.091723768948589</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.09172376894858913</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>607522.6002570402</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.3012208034455313</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>200.08788953645572</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>607522.6002570402</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>260.8820298724062</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$173,A12,'Species'!$U$2:$U$173))</x:f>
-        <x:v>158491729.14841905</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.3012208034455313</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>200.08788953645572</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>121557914.931131</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>36933814.21728805</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3038371811347127</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.3038371811347127</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>500716.6775091781</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.648023093675365</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>444.6549114332541</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>500716.6775091781</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>797.3339285117717</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$173,A13,'Species'!$U$2:$U$173))</x:f>
-        <x:v>399238395.54975486</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.648023093675365</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>444.6549114332541</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>222646129.89099684</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>176592265.658758</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.793152190631897</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.7931521906318969</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>100428.749794478</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.221279893009376</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>166.44850278727986</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>100428.749794478</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>348.60180625914404</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$173,A14,'Species'!$U$2:$U$173))</x:f>
-        <x:v>35009643.57870267</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.221279893009376</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>166.44850278727986</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>16716215.040089205</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>18293428.53861347</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.0943523097029892</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.0943523097029892</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>186261.58284665536</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.4216150763812516</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>26.400677767948114</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>186261.58284665536</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>26.56570562241469</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$173,A15,'Species'!$U$2:$U$173))</x:f>
-        <x:v>4948170.378669252</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.4216150763812516</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>26.400677767948114</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>4917432.0292825205</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>30738.349386731163</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0062508946140363</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.006250894614036191</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>23355.252147586998</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.9878495637630085</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>97.24103300423914</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>23355.252147586998</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>123.37333113809235</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$173,A16,'Species'!$U$2:$U$173))</x:f>
-        <x:v>2881415.2570178933</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.9878495637630085</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>97.24103300423914</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>2271088.844905834</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>610326.4121120591</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.2687373563042466</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.2687373563042466</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>49250.6832747155</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.2318544545835928</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>170.55107242038721</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>49250.6832747155</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>175.02531140135088</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$173,A17,'Species'!$U$2:$U$173))</x:f>
-        <x:v>8620116.176886383</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.2318544545835928</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>170.55107242038721</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>8399756.849939557</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>220359.32694682665</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0262340125891158</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.026234012589115875</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>4853.770573878</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.4287557070153576</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>268.38343497062573</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>4853.770573878</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>275.59475092149563</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$173,A18,'Species'!$U$2:$U$173))</x:f>
-        <x:v>1337673.6923379921</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.4287557070153576</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>268.38343497062573</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>1302671.6191767228</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>35002.073161269305</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0268694524744388</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.026869452474438886</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>400875.5302457502</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.831318467140663</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>67.81386028004302</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>400875.5302457502</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>76.67139839667323</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$173,A19,'Species'!$U$2:$U$173))</x:f>
-        <x:v>30735687.48694954</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.831318467140663</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>67.81386028004302</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>27184917.197773464</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>3550770.2891760767</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1306154535378499</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.1306154535378499</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>31794.9580405562</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.3777265254428546</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>238.63081551849248</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>31794.9580405562</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>330.75139324905814</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$173,A20,'Species'!$U$2:$U$173))</x:f>
-        <x:v>10516226.670209307</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.3777265254428546</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>238.63081551849248</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>7587256.766594176</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>2928969.903615131</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.3860380627305313</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.3860380627305314</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>1124.4953723791</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>4.058196871183961</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>1143.3965334443915</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>1124.4953723791</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>1145.2957786348377</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$173,A21,'Species'!$U$2:$U$173))</x:f>
-        <x:v>1287879.803080193</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>4.058196871183961</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>1143.3965334443915</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>1285744.110652523</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>2135.6924276698846</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0016610555786143</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.0016610555786143227</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R418a8074eb2d43e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81ccfbca09084f65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14193,7 +12989,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -14292,7 +13088,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1117733410.4784863</x:v>
+        <x:v>863818470.0629802</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14306,7 +13102,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1117733410.478486</x:v>
+        <x:v>865862679.5151173</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14320,7 +13116,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>2.384185791015625e-7</x:v>
+        <x:v>-253914940.4155059</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14334,7 +13130,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-251870730.96336877</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14345,9 +13141,9 @@
         <x:v>EEZ_608</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -14359,47 +13155,19 @@
         <x:v>EEZ_608</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_608</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_608</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re08da032ea654a47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf160c8062ae74349"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14446,7 +13214,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
